--- a/docs/workbook-split/dateien/Monatsroll.xlsx
+++ b/docs/workbook-split/dateien/Monatsroll.xlsx
@@ -691,65 +691,34 @@
       <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
-        <f>IF(C7&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C7)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F7" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C7)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G7" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C7)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C7,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H7" s="8">
-        <f>SUM(E7:F7)-G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>IF(D7="IST","",IF(C7='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q6))</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>IF(D7="IST","",IF(C7-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C7-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K7" s="7">
-        <f>IF(D7="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>IF(D7="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C7))</f>
-        <v/>
-      </c>
-      <c r="M7" s="7">
-        <f>IF(D7="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C7,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="7">
-        <f>IF(D7="IST","",IF(C7-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C7-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O7" s="7">
-        <f>IF(D7="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P7" s="7">
-        <f>IF(D7="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C7,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8">
-        <f>IF(D7="IST","",IF(OR(J7="n.a.",N7="n.a."),"n.a.",SUM(I7:M7)-SUM(N7:O7)+P7))</f>
-        <v/>
-      </c>
-      <c r="R7" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C7)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C7))</f>
-        <v/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>639565.45</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1280847.26</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>294942.37</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1625470.34</v>
+      </c>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="7" t="n">
+        <v>-967394.51</v>
       </c>
       <c r="S7" s="1" t="n"/>
       <c r="T7" s="1" t="n"/>
@@ -760,65 +729,34 @@
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
-        <f>IF(C8&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C8)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F8" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C8)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G8" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C8)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C8,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H8" s="8">
-        <f>SUM(E8:F8)-G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>IF(D8="IST","",IF(C8='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q7))</f>
-        <v/>
-      </c>
-      <c r="J8" s="7">
-        <f>IF(D8="IST","",IF(C8-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C8-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
-        <f>IF(D8="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>IF(D8="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C8))</f>
-        <v/>
-      </c>
-      <c r="M8" s="7">
-        <f>IF(D8="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C8,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="7">
-        <f>IF(D8="IST","",IF(C8-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C8-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O8" s="7">
-        <f>IF(D8="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P8" s="7">
-        <f>IF(D8="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C8,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="8">
-        <f>IF(D8="IST","",IF(OR(J8="n.a.",N8="n.a."),"n.a.",SUM(I8:M8)-SUM(N8:O8)+P8))</f>
-        <v/>
-      </c>
-      <c r="R8" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C8)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C8))</f>
-        <v/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2777244.65</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>-200176.92</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>318570.76</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>2258496.97</v>
+      </c>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="7" t="n">
+        <v>-1687613.22</v>
       </c>
       <c r="S8" s="1" t="n"/>
       <c r="T8" s="1" t="n"/>
@@ -829,65 +767,34 @@
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6">
-        <f>IF(C9&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E9" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C9)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F9" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C9)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G9" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C9)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C9,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H9" s="8">
-        <f>SUM(E9:F9)-G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>IF(D9="IST","",IF(C9='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q8))</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>IF(D9="IST","",IF(C9-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C9-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="7">
-        <f>IF(D9="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L9" s="7">
-        <f>IF(D9="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C9))</f>
-        <v/>
-      </c>
-      <c r="M9" s="7">
-        <f>IF(D9="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C9,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N9" s="7">
-        <f>IF(D9="IST","",IF(C9-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C9-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O9" s="7">
-        <f>IF(D9="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P9" s="7">
-        <f>IF(D9="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C9,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="8">
-        <f>IF(D9="IST","",IF(OR(J9="n.a.",N9="n.a."),"n.a.",SUM(I9:M9)-SUM(N9:O9)+P9))</f>
-        <v/>
-      </c>
-      <c r="R9" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C9)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C9))</f>
-        <v/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1213541.38</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1198671.49</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>23595.18</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>2388617.69</v>
+      </c>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="7" t="n">
+        <v>-1081708.41</v>
       </c>
       <c r="S9" s="1" t="n"/>
       <c r="T9" s="1" t="n"/>
@@ -898,65 +805,34 @@
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
-        <f>IF(C10&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C10)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F10" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C10)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G10" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C10)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C10,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>SUM(E10:F10)-G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>IF(D10="IST","",IF(C10='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q9))</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>IF(D10="IST","",IF(C10-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C10-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="7">
-        <f>IF(D10="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>IF(D10="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C10))</f>
-        <v/>
-      </c>
-      <c r="M10" s="7">
-        <f>IF(D10="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C10,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N10" s="7">
-        <f>IF(D10="IST","",IF(C10-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C10-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O10" s="7">
-        <f>IF(D10="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P10" s="7">
-        <f>IF(D10="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C10,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="8">
-        <f>IF(D10="IST","",IF(OR(J10="n.a.",N10="n.a."),"n.a.",SUM(I10:M10)-SUM(N10:O10)+P10))</f>
-        <v/>
-      </c>
-      <c r="R10" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C10)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C10))</f>
-        <v/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>678343.59</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1261219.89</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>-179274.07</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>2118837.55</v>
+      </c>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="7" t="n">
+        <v>-1858253.62</v>
       </c>
       <c r="S10" s="1" t="n"/>
       <c r="T10" s="1" t="n"/>
@@ -967,65 +843,34 @@
       <c r="C11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="6">
-        <f>IF(C11&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C11)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F11" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C11)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G11" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C11)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C11,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H11" s="8">
-        <f>SUM(E11:F11)-G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>IF(D11="IST","",IF(C11='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q10))</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>IF(D11="IST","",IF(C11-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C11-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="7">
-        <f>IF(D11="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L11" s="7">
-        <f>IF(D11="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="7">
-        <f>IF(D11="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C11,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N11" s="7">
-        <f>IF(D11="IST","",IF(C11-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C11-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O11" s="7">
-        <f>IF(D11="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P11" s="7">
-        <f>IF(D11="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C11,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="8">
-        <f>IF(D11="IST","",IF(OR(J11="n.a.",N11="n.a."),"n.a.",SUM(I11:M11)-SUM(N11:O11)+P11))</f>
-        <v/>
-      </c>
-      <c r="R11" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C11)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C11))</f>
-        <v/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1347585.48</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>-263604.09</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-141241.9</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1225223.29</v>
+      </c>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="7" t="n">
+        <v>-2445311.2</v>
       </c>
       <c r="S11" s="1" t="n"/>
       <c r="T11" s="1" t="n"/>
@@ -1036,65 +881,34 @@
       <c r="C12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="6">
-        <f>IF(C12&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E12" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C12)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F12" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C12)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G12" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C12)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C12,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>SUM(E12:F12)-G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="7">
-        <f>IF(D12="IST","",IF(C12='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q11))</f>
-        <v/>
-      </c>
-      <c r="J12" s="7">
-        <f>IF(D12="IST","",IF(C12-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C12-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="7">
-        <f>IF(D12="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L12" s="7">
-        <f>IF(D12="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C12))</f>
-        <v/>
-      </c>
-      <c r="M12" s="7">
-        <f>IF(D12="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C12,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N12" s="7">
-        <f>IF(D12="IST","",IF(C12-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C12-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O12" s="7">
-        <f>IF(D12="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P12" s="7">
-        <f>IF(D12="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C12,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8">
-        <f>IF(D12="IST","",IF(OR(J12="n.a.",N12="n.a."),"n.a.",SUM(I12:M12)-SUM(N12:O12)+P12))</f>
-        <v/>
-      </c>
-      <c r="R12" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C12)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C12))</f>
-        <v/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>2470042.1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>314645.23</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>58553.86</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>2726133.47</v>
+      </c>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="7" t="n">
+        <v>-1778289.46</v>
       </c>
       <c r="S12" s="1" t="n"/>
       <c r="T12" s="1" t="n"/>
@@ -1105,65 +919,34 @@
       <c r="C13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="6">
-        <f>IF(C13&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E13" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C13)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F13" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C13)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G13" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C13)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C13,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H13" s="8">
-        <f>SUM(E13:F13)-G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="7">
-        <f>IF(D13="IST","",IF(C13='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q12))</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>IF(D13="IST","",IF(C13-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C13-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="7">
-        <f>IF(D13="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L13" s="7">
-        <f>IF(D13="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="7">
-        <f>IF(D13="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C13,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N13" s="7">
-        <f>IF(D13="IST","",IF(C13-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C13-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O13" s="7">
-        <f>IF(D13="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P13" s="7">
-        <f>IF(D13="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C13,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="8">
-        <f>IF(D13="IST","",IF(OR(J13="n.a.",N13="n.a."),"n.a.",SUM(I13:M13)-SUM(N13:O13)+P13))</f>
-        <v/>
-      </c>
-      <c r="R13" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C13)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C13))</f>
-        <v/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1323928.2</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>294716.46</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>-495291.54</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2113936.2</v>
+      </c>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="7" t="n">
+        <v>-919229.04</v>
       </c>
       <c r="S13" s="1" t="n"/>
       <c r="T13" s="1" t="n"/>
@@ -1174,65 +957,34 @@
       <c r="C14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
-        <f>IF(C14&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E14" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C14)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F14" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C14)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G14" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C14)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C14,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H14" s="8">
-        <f>SUM(E14:F14)-G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="7">
-        <f>IF(D14="IST","",IF(C14='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q13))</f>
-        <v/>
-      </c>
-      <c r="J14" s="7">
-        <f>IF(D14="IST","",IF(C14-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C14-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="7">
-        <f>IF(D14="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L14" s="7">
-        <f>IF(D14="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="7">
-        <f>IF(D14="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C14,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N14" s="7">
-        <f>IF(D14="IST","",IF(C14-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C14-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O14" s="7">
-        <f>IF(D14="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P14" s="7">
-        <f>IF(D14="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C14,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="8">
-        <f>IF(D14="IST","",IF(OR(J14="n.a.",N14="n.a."),"n.a.",SUM(I14:M14)-SUM(N14:O14)+P14))</f>
-        <v/>
-      </c>
-      <c r="R14" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C14)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C14))</f>
-        <v/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1022525.14</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>2015107.35</v>
+      </c>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="7" t="n">
+        <v>1944327.5</v>
       </c>
       <c r="S14" s="1" t="n"/>
       <c r="T14" s="1" t="n"/>
@@ -1243,66 +995,51 @@
       <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="6">
-        <f>IF(C15&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E15" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C15)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F15" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C15)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G15" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C15)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C15,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H15" s="8">
-        <f>SUM(E15:F15)-G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="7">
-        <f>IF(D15="IST","",IF(C15='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q14))</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>IF(D15="IST","",IF(C15-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C15-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K15" s="7">
-        <f>IF(D15="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L15" s="7">
-        <f>IF(D15="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="7">
-        <f>IF(D15="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C15,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N15" s="7">
-        <f>IF(D15="IST","",IF(C15-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C15-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O15" s="7">
-        <f>IF(D15="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P15" s="7">
-        <f>IF(D15="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C15,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="8">
-        <f>IF(D15="IST","",IF(OR(J15="n.a.",N15="n.a."),"n.a.",SUM(I15:M15)-SUM(N15:O15)+P15))</f>
-        <v/>
-      </c>
-      <c r="R15" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C15)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C15))</f>
-        <v/>
-      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>PLAN</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>2604944</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>468444</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2136500</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>1944327.5</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1347585.48</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>209759.08</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>1671763.97</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>337946.2</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>1491961.89</v>
+      </c>
+      <c r="R15" s="7" t="n"/>
       <c r="S15" s="1" t="n"/>
       <c r="T15" s="1" t="n"/>
     </row>
@@ -1312,66 +1049,51 @@
       <c r="C16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="6">
-        <f>IF(C16&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E16" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C16)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F16" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C16)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G16" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C16)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C16,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H16" s="8">
-        <f>SUM(E16:F16)-G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="7">
-        <f>IF(D16="IST","",IF(C16='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q15))</f>
-        <v/>
-      </c>
-      <c r="J16" s="7">
-        <f>IF(D16="IST","",IF(C16-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C16-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K16" s="7">
-        <f>IF(D16="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L16" s="7">
-        <f>IF(D16="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C16))</f>
-        <v/>
-      </c>
-      <c r="M16" s="7">
-        <f>IF(D16="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C16,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N16" s="7">
-        <f>IF(D16="IST","",IF(C16-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C16-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O16" s="7">
-        <f>IF(D16="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P16" s="7">
-        <f>IF(D16="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C16,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="8">
-        <f>IF(D16="IST","",IF(OR(J16="n.a.",N16="n.a."),"n.a.",SUM(I16:M16)-SUM(N16:O16)+P16))</f>
-        <v/>
-      </c>
-      <c r="R16" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C16)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C16))</f>
-        <v/>
-      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>PLAN</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1333000</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>261250</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>1071750</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1491961.89</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>2470042.1</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>209759.08</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>1793156.62</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>337946.2</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>2040660.25</v>
+      </c>
+      <c r="R16" s="7" t="n"/>
       <c r="S16" s="1" t="n"/>
       <c r="T16" s="1" t="n"/>
     </row>
@@ -1381,66 +1103,51 @@
       <c r="C17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="6">
-        <f>IF(C17&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E17" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C17)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F17" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C17)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G17" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C17)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C17,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H17" s="8">
-        <f>SUM(E17:F17)-G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="7">
-        <f>IF(D17="IST","",IF(C17='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q16))</f>
-        <v/>
-      </c>
-      <c r="J17" s="7">
-        <f>IF(D17="IST","",IF(C17-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C17-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K17" s="7">
-        <f>IF(D17="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L17" s="7">
-        <f>IF(D17="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C17))</f>
-        <v/>
-      </c>
-      <c r="M17" s="7">
-        <f>IF(D17="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C17,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N17" s="7">
-        <f>IF(D17="IST","",IF(C17-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C17-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O17" s="7">
-        <f>IF(D17="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P17" s="7">
-        <f>IF(D17="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C17,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="8">
-        <f>IF(D17="IST","",IF(OR(J17="n.a.",N17="n.a."),"n.a.",SUM(I17:M17)-SUM(N17:O17)+P17))</f>
-        <v/>
-      </c>
-      <c r="R17" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C17)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C17))</f>
-        <v/>
-      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>PLAN</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1775000</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>516650</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1258350</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>2040660.25</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>1323928.2</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>209759.08</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>728406.62</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>337946.2</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>2507994.71</v>
+      </c>
+      <c r="R17" s="7" t="n"/>
       <c r="S17" s="1" t="n"/>
       <c r="T17" s="1" t="n"/>
     </row>
@@ -1450,66 +1157,51 @@
       <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="6">
-        <f>IF(C18&lt;'[Steuerung.xlsx]Steuerung'!$F$50,"IST","PLAN")</f>
-        <v/>
-      </c>
-      <c r="E18" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$632:$C$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C18)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="F18" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$632:$D$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C18)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="G18" s="7">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$E$632:$E$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,C18)+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$G$7:$G$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")+SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$H$7:$H$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")-SUMIFS('[FC Eingabe.xlsx]FC Eingabe'!$I$7:$I$506,'[FC Eingabe.xlsx]FC Eingabe'!$C$7:$C$506,'[Steuerung.xlsx]Steuerung'!$F$6,'[FC Eingabe.xlsx]FC Eingabe'!$D$7:$D$506,C18,'[FC Eingabe.xlsx]FC Eingabe'!$K$7:$K$506,"Wirksam")</f>
-        <v/>
-      </c>
-      <c r="H18" s="8">
-        <f>SUM(E18:F18)-G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="7">
-        <f>IF(D18="IST","",IF(C18='[Steuerung.xlsx]Steuerung'!$F$50,'[Steuerung.xlsx]Steuerung'!$F$51,Q17))</f>
-        <v/>
-      </c>
-      <c r="J18" s="7">
-        <f>IF(D18="IST","",IF(C18-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($E$7:$E$18,C18-ROUND('[Steuerung.xlsx]Steuerung'!$F$36/'[Steuerung.xlsx]Steuerung'!$F$40,0))))</f>
-        <v/>
-      </c>
-      <c r="K18" s="7">
-        <f>IF(D18="IST","",'[Steuerung.xlsx]Steuerung'!$F$38)</f>
-        <v/>
-      </c>
-      <c r="L18" s="7">
-        <f>IF(D18="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$674:$D$676,'[D Liquidität.xlsx]D Liquidität'!$A$674:$A$676,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$674:$B$676,C18))</f>
-        <v/>
-      </c>
-      <c r="M18" s="7">
-        <f>IF(D18="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C18,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&gt;0"))</f>
-        <v/>
-      </c>
-      <c r="N18" s="7">
-        <f>IF(D18="IST","",IF(C18-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0)&lt;1,"n.a.",INDEX($H$7:$H$18,C18-ROUND('[Steuerung.xlsx]Steuerung'!$F$37/'[Steuerung.xlsx]Steuerung'!$F$40,0))-'[Steuerung.xlsx]Steuerung'!$F$41-'[Steuerung.xlsx]Steuerung'!$F$42))</f>
-        <v/>
-      </c>
-      <c r="O18" s="7">
-        <f>IF(D18="IST","",'[Steuerung.xlsx]Steuerung'!$F$41+'[Steuerung.xlsx]Steuerung'!$F$43+'[Steuerung.xlsx]Steuerung'!$F$45+'[Steuerung.xlsx]Steuerung'!$F$46)</f>
-        <v/>
-      </c>
-      <c r="P18" s="7">
-        <f>IF(D18="IST","",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,'[D Liquidität.xlsx]D Liquidität'!$A$91:$A$191,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$91:$B$191,C18,'[D Liquidität.xlsx]D Liquidität'!$I$91:$I$191,"&lt;&gt;CHANCE",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;ERLEDIGT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;GEZAHLT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;STORNIERT",'[D Liquidität.xlsx]D Liquidität'!$H$91:$H$191,"&lt;&gt;VERLOREN",'[D Liquidität.xlsx]D Liquidität'!$D$91:$D$191,"&lt;0"))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="8">
-        <f>IF(D18="IST","",IF(OR(J18="n.a.",N18="n.a."),"n.a.",SUM(I18:M18)-SUM(N18:O18)+P18))</f>
-        <v/>
-      </c>
-      <c r="R18" s="7">
-        <f>IF(COUNTIFS('[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C18)=0,"",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$C$661:$C$668,'[D Liquidität.xlsx]D Liquidität'!$A$661:$A$668,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$661:$B$668,C18))</f>
-        <v/>
-      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>PLAN</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1073000</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>26153</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1046847</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>2507994.71</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>209759.08</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>915006.62</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>337946.2</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>2319140.81</v>
+      </c>
+      <c r="R18" s="7" t="n"/>
       <c r="S18" s="1" t="n"/>
       <c r="T18" s="1" t="n"/>
     </row>
@@ -2410,6 +2102,8 @@
       <c r="S60" s="1" t="n"/>
       <c r="T60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
